--- a/tests/v1/fixtures/office6m/2026-06/bank_statements/TCB_HOLD_USD_2026-05.xlsx
+++ b/tests/v1/fixtures/office6m/2026-06/bank_statements/TCB_HOLD_USD_2026-05.xlsx
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>198829.25</v>
+        <v>202809.25</v>
       </c>
       <c r="E2" t="n">
         <v>239.06</v>
       </c>
       <c r="F2" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="3">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="4">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="5">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="6">
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="7">
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="8">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="9">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="10">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="11">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="12">
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="14">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="15">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="16">
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="17">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="18">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="19">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="20">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
     </row>
     <row r="21">
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>199068.31</v>
+        <v>203048.31</v>
       </c>
       <c r="E21" t="n">
         <v>-32.29</v>
       </c>
       <c r="F21" t="n">
-        <v>199036.02</v>
+        <v>203016.02</v>
       </c>
     </row>
     <row r="22">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>199036.02</v>
+        <v>203016.02</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>199036.02</v>
+        <v>203016.02</v>
       </c>
     </row>
   </sheetData>
